--- a/website_content_creation/authors/Ambre_Audebert/Author_form.xlsx
+++ b/website_content_creation/authors/Ambre_Audebert/Author_form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://041gc-my.sharepoint.com/personal/emily_smenderovac_nrcan-rncan_gc_ca/Documents/Documents/WET lab/GLFC-WET.github.io/website_content_creation/authors/Ambre_Audebert/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{119D785A-2014-0942-9DEE-F753A1092E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B8461F1-99B1-4210-8AB1-C880244BC474}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{119D785A-2014-0942-9DEE-F753A1092E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68E48222-5C72-4061-820C-365A5BC27AF8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16080" yWindow="-14805" windowWidth="27000" windowHeight="14040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -135,9 +135,6 @@
     <t xml:space="preserve">Ambre Audebert </t>
   </si>
   <si>
-    <t xml:space="preserve">master degree student, UQAT </t>
-  </si>
-  <si>
     <t>https://www.instagram.com/ambre_adb</t>
   </si>
   <si>
@@ -175,6 +172,9 @@
   </si>
   <si>
     <t>Visiting and Co-supervised Students</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc student, UQAT </t>
   </si>
 </sst>
 </file>
@@ -864,7 +864,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -881,7 +881,7 @@
         <v>27</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -892,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -941,7 +941,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -961,7 +961,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
@@ -992,10 +992,10 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="12">
         <v>2024</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>39</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>40</v>
       </c>
       <c r="C21" s="13">
         <v>2027</v>
@@ -1044,10 +1044,10 @@
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1082,17 +1082,17 @@
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
